--- a/data/trans_camb/P2A_ner_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P2A_ner_R-Provincia-trans_camb.xlsx
@@ -614,7 +614,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,29; 6,42</t>
+          <t>-8,09; 6,72</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,42; 14,44</t>
+          <t>-1,84; 13,83</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-11,08; 0,39</t>
+          <t>-11,59; 0,52</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-14,03; 2,04</t>
+          <t>-14,5; 1,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-10,35; 6,77</t>
+          <t>-11,22; 6,17</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-16,6; -2,91</t>
+          <t>-16,65; -3,77</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-9,45; 1,73</t>
+          <t>-9,61; 1,21</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-5,03; 7,46</t>
+          <t>-5,11; 7,12</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-10,88; -2,65</t>
+          <t>-10,82; -2,69</t>
         </is>
       </c>
     </row>
@@ -788,22 +788,22 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-54,47; 687,63</t>
+          <t>-42,67; 752,43</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 159,03</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-84,36; 220,55</t>
+          <t>-86,2; 234,48</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -813,24 +813,24 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 92,71</t>
+          <t>-100,0; 60,16</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-53,49; 196,66</t>
+          <t>-53,33; 167,26</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -51,28</t>
+          <t>-100,0; -46,82</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 7,2</t>
+          <t>-2,17; 7,25</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 8,62</t>
+          <t>-0,91; 9,89</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 6,5</t>
+          <t>-1,99; 6,59</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,85; 0,0</t>
+          <t>-6,86; 0,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 8,62</t>
+          <t>-1,25; 7,86</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 5,48</t>
+          <t>-1,77; 6,1</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 2,45</t>
+          <t>-2,36; 2,8</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,24; 7,01</t>
+          <t>0,05; 7,1</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 4,92</t>
+          <t>-0,69; 4,84</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-51,08; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-70,21; —</t>
+          <t>-70,8; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1019,34 +1019,34 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-60,95; —</t>
+          <t>-67,58; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-67,85; —</t>
+          <t>-67,17; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 472,5</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-15,44; 984,67</t>
+          <t>-18,23; 964,61</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-35,33; 778,7</t>
+          <t>-34,2; 712,3</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,03; 0,0</t>
+          <t>-5,31; 0,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 4,65</t>
+          <t>-2,11; 4,36</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 5,06</t>
+          <t>-2,09; 5,37</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,32; 0,0</t>
+          <t>-4,83; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,2; 10,82</t>
+          <t>0,22; 10,05</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,73; 10,1</t>
+          <t>0,6; 9,7</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 0,0</t>
+          <t>-3,31; 0,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 6,05</t>
+          <t>-0,11; 6,53</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,05; 5,9</t>
+          <t>-0,0; 6,08</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-72,38; —</t>
+          <t>-62,27; —</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-48,23; —</t>
+          <t>-50,67; —</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,01; 12,41</t>
+          <t>-0,62; 11,97</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,26; 14,08</t>
+          <t>0,64; 14,21</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 4,48</t>
+          <t>-3,05; 4,55</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 8,21</t>
+          <t>-2,2; 8,62</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,12; 20,86</t>
+          <t>2,58; 21,4</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-7,59; 0,0</t>
+          <t>-6,49; 0,0</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,22; 8,35</t>
+          <t>-0,01; 8,61</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,47; 14,6</t>
+          <t>3,39; 14,8</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 1,29</t>
+          <t>-3,43; 1,19</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-22,58; —</t>
+          <t>4,36; —</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1461,12 +1461,12 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-41,52; inf</t>
+          <t>-39,38; 1864,5</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>60,94; 2243,69</t>
+          <t>62,55; 2710,92</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-12,84; 22,1</t>
+          <t>-13,22; 24,16</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-21,71; 10,74</t>
+          <t>-18,09; 12,83</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-26,48; 3,24</t>
+          <t>-24,7; 3,31</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,19</t>
+          <t>0,0; 14,23</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,68; 14,88</t>
+          <t>1,67; 15,5</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,36</t>
+          <t>0,0; 7,48</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-4,55; 11,96</t>
+          <t>-4,52; 11,88</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-5,24; 10,56</t>
+          <t>-5,16; 10,15</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-11,27; 2,41</t>
+          <t>-13,73; 2,33</t>
         </is>
       </c>
     </row>
@@ -1694,7 +1694,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,13</t>
+          <t>0,0; 11,17</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,17</t>
+          <t>0,0; 15,93</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1,1; 11,71</t>
+          <t>1,13; 10,63</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-7,16; 0,0</t>
+          <t>-8,3; 0,0</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 11,73</t>
+          <t>-3,49; 12,06</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-4,72; 4,91</t>
+          <t>-4,05; 5,07</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 2,65</t>
+          <t>-2,02; 3,25</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>0,39; 10,27</t>
+          <t>-0,22; 10,13</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 5,7</t>
+          <t>-0,69; 5,9</t>
         </is>
       </c>
     </row>
@@ -1898,19 +1898,19 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-76,9; —</t>
+          <t>-63,65; —</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 2,22</t>
+          <t>-2,63; 2,24</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 6,24</t>
+          <t>-0,75; 5,99</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0,87; 8,55</t>
+          <t>0,98; 8,4</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 2,07</t>
+          <t>-3,87; 1,71</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-4,23; 1,82</t>
+          <t>-3,75; 2,33</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,19; 10,57</t>
+          <t>1,28; 11,44</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 1,33</t>
+          <t>-2,34; 1,33</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 2,82</t>
+          <t>-1,38; 3,08</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>2,04; 8,57</t>
+          <t>2,26; 8,46</t>
         </is>
       </c>
     </row>
@@ -2084,42 +2084,42 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-79,33; —</t>
+          <t>-79,08; —</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-12,44; —</t>
+          <t>-35,46; —</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 239,49</t>
+          <t>-100,0; 289,52</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 356,37</t>
+          <t>-100,0; 549,92</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>3,4; 1172,77</t>
+          <t>8,55; 1458,37</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-81,61; 205,49</t>
+          <t>-79,82; 230,63</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-60,27; 308,07</t>
+          <t>-59,23; 364,28</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>44,82; 912,56</t>
+          <t>49,24; 952,36</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-5,02; 3,16</t>
+          <t>-5,37; 3,22</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-4,33; 4,15</t>
+          <t>-4,69; 4,33</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>3,3; 15,85</t>
+          <t>3,14; 15,41</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-5,81; 0,58</t>
+          <t>-5,75; 0,48</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 3,97</t>
+          <t>-3,7; 4,06</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>4,6; 15,96</t>
+          <t>4,71; 16,22</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 0,95</t>
+          <t>-4,25; 1,04</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 2,95</t>
+          <t>-2,2; 3,35</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>5,93; 13,84</t>
+          <t>5,83; 13,93</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-82,51; 207,43</t>
+          <t>-82,81; 199,61</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-65,03; 242,1</t>
+          <t>-69,04; 238,09</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>36,24; 746,94</t>
+          <t>34,29; 844,69</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 156,31</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-71,91; 309,91</t>
+          <t>-77,33; 347,42</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>60,07; 1184,99</t>
+          <t>70,0; 1254,28</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-81,61; 61,61</t>
+          <t>-81,28; 62,62</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-52,47; 138,69</t>
+          <t>-45,43; 164,65</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>98,3; 664,3</t>
+          <t>106,27; 717,11</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 2,54</t>
+          <t>-0,82; 2,5</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>1,05; 4,86</t>
+          <t>0,99; 4,77</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1,38; 4,98</t>
+          <t>1,49; 5,04</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-2,86; -0,02</t>
+          <t>-2,64; -0,01</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>0,29; 3,88</t>
+          <t>0,24; 3,91</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,14; 5,06</t>
+          <t>1,29; 4,83</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 0,74</t>
+          <t>-1,36; 0,73</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>1,19; 3,81</t>
+          <t>1,08; 3,65</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>1,82; 4,43</t>
+          <t>1,86; 4,41</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-26,92; 162,54</t>
+          <t>-30,3; 154,55</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>31,39; 321,6</t>
+          <t>22,01; 305,45</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>39,92; 339,12</t>
+          <t>44,25; 343,91</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-79,12; 3,74</t>
+          <t>-76,48; 7,11</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>4,51; 207,97</t>
+          <t>5,83; 202,8</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>31,01; 269,31</t>
+          <t>35,55; 239,55</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-44,46; 38,9</t>
+          <t>-46,46; 37,6</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>38,33; 195,61</t>
+          <t>35,97; 184,39</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>60,49; 224,23</t>
+          <t>58,08; 229,53</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2A_ner_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P2A_ner_R-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,09; 6,72</t>
+          <t>-8,82; 6,47</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 13,83</t>
+          <t>-2,59; 14,59</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-11,59; 0,52</t>
+          <t>-10,33; 0,75</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-14,5; 1,0</t>
+          <t>-14,67; 1,32</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-11,22; 6,17</t>
+          <t>-11,47; 5,81</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-16,65; -3,77</t>
+          <t>-17,87; -3,82</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-9,61; 1,21</t>
+          <t>-9,2; 1,06</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-5,11; 7,12</t>
+          <t>-4,51; 7,18</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-10,82; -2,69</t>
+          <t>-11,35; -2,77</t>
         </is>
       </c>
     </row>
@@ -788,22 +788,22 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-42,67; 752,43</t>
+          <t>-48,12; 658,23</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 159,03</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 237,14</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-86,2; 234,48</t>
+          <t>-85,47; 226,82</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 60,16</t>
+          <t>-100,0; 87,9</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-53,33; 167,26</t>
+          <t>-51,05; 182,14</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -46,82</t>
+          <t>-100,0; -47,79</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 7,25</t>
+          <t>-2,46; 7,45</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 9,89</t>
+          <t>-0,97; 9,13</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 6,59</t>
+          <t>-1,74; 7,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,86; 0,0</t>
+          <t>-6,97; 0,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 7,86</t>
+          <t>-1,23; 8,68</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 6,1</t>
+          <t>-1,91; 5,26</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 2,8</t>
+          <t>-2,4; 2,5</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,05; 7,1</t>
+          <t>0,15; 7,37</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 4,84</t>
+          <t>-0,88; 4,77</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-51,08; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-70,8; —</t>
+          <t>-68,85; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1019,12 +1019,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-67,58; —</t>
+          <t>-69,33; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-67,17; —</t>
+          <t>-60,05; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1034,12 +1034,12 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-18,23; 964,61</t>
+          <t>-23,97; 1011,4</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-34,2; 712,3</t>
+          <t>-32,0; 773,52</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,31; 0,0</t>
+          <t>-5,81; 0,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 4,36</t>
+          <t>-2,11; 5,71</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 5,37</t>
+          <t>-2,11; 5,27</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,83; 0,0</t>
+          <t>-4,7; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,22; 10,05</t>
+          <t>0,49; 10,87</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,6; 9,7</t>
+          <t>0,58; 10,72</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 0,0</t>
+          <t>-3,45; 0,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 6,53</t>
+          <t>-0,14; 6,35</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,0; 6,08</t>
+          <t>0,14; 6,23</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-62,27; —</t>
+          <t>-72,84; —</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-50,67; —</t>
+          <t>-45,78; —</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 11,97</t>
+          <t>0,0; 12,88</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,64; 14,21</t>
+          <t>0,46; 13,98</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 4,55</t>
+          <t>-2,82; 4,38</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 8,62</t>
+          <t>-2,38; 9,03</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,58; 21,4</t>
+          <t>2,13; 20,51</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-6,49; 0,0</t>
+          <t>-6,44; 0,0</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 8,61</t>
+          <t>-0,03; 8,27</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,39; 14,8</t>
+          <t>3,18; 14,13</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 1,19</t>
+          <t>-3,74; 1,26</t>
         </is>
       </c>
     </row>
@@ -1446,12 +1446,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,36; —</t>
+          <t>-30,16; —</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1461,12 +1461,12 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-39,38; 1864,5</t>
+          <t>-25,37; 1351,26</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>62,55; 2710,92</t>
+          <t>44,03; 2791,22</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-13,22; 24,16</t>
+          <t>-12,94; 22,95</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-18,09; 12,83</t>
+          <t>-18,01; 12,71</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-24,7; 3,31</t>
+          <t>-26,78; 3,3</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,23</t>
+          <t>0,0; 15,33</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,67; 15,5</t>
+          <t>1,68; 15,27</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,48</t>
+          <t>0,0; 6,85</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-4,52; 11,88</t>
+          <t>-5,88; 12,01</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-5,16; 10,15</t>
+          <t>-5,27; 10,41</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-13,73; 2,33</t>
+          <t>-12,39; 2,4</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,17</t>
+          <t>0,0; 8,95</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,93</t>
+          <t>0,0; 16,26</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1,13; 10,63</t>
+          <t>1,1; 10,63</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-8,3; 0,0</t>
+          <t>-8,28; 0,0</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 12,06</t>
+          <t>-3,52; 11,83</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 5,07</t>
+          <t>-3,99; 5,14</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 3,25</t>
+          <t>-2,49; 2,97</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 10,13</t>
+          <t>-0,15; 10,3</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 5,9</t>
+          <t>-0,73; 5,71</t>
         </is>
       </c>
     </row>
@@ -1903,7 +1903,7 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-63,65; —</t>
+          <t>-55,99; —</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 2,24</t>
+          <t>-2,58; 2,18</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 5,99</t>
+          <t>-0,81; 6,14</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0,98; 8,4</t>
+          <t>1,0; 8,6</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-3,87; 1,71</t>
+          <t>-4,16; 1,99</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 2,33</t>
+          <t>-4,2; 1,95</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,28; 11,44</t>
+          <t>1,03; 11,23</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 1,33</t>
+          <t>-2,51; 1,58</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 3,08</t>
+          <t>-1,32; 3,05</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>2,26; 8,46</t>
+          <t>2,11; 8,55</t>
         </is>
       </c>
     </row>
@@ -2084,42 +2084,42 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-79,08; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-35,46; —</t>
+          <t>-11,45; —</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 289,52</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 549,92</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>8,55; 1458,37</t>
+          <t>2,96; 1221,11</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-79,82; 230,63</t>
+          <t>-81,69; 268,8</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-59,23; 364,28</t>
+          <t>-54,31; 388,12</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>49,24; 952,36</t>
+          <t>65,68; 1107,71</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-5,37; 3,22</t>
+          <t>-5,69; 2,9</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-4,69; 4,33</t>
+          <t>-4,26; 4,11</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>3,14; 15,41</t>
+          <t>4,02; 15,53</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-5,75; 0,48</t>
+          <t>-5,37; 0,6</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-3,7; 4,06</t>
+          <t>-3,33; 4,05</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>4,71; 16,22</t>
+          <t>5,02; 15,59</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-4,25; 1,04</t>
+          <t>-4,52; 0,68</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 3,35</t>
+          <t>-2,33; 3,26</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>5,83; 13,93</t>
+          <t>5,87; 13,8</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-82,81; 199,61</t>
+          <t>-83,32; 226,07</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-69,04; 238,09</t>
+          <t>-68,26; 225,91</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>34,29; 844,69</t>
+          <t>43,94; 897,62</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 169,02</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-77,33; 347,42</t>
+          <t>-69,62; 356,66</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>70,0; 1254,28</t>
+          <t>74,26; 1227,14</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-81,28; 62,62</t>
+          <t>-83,13; 45,33</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-45,43; 164,65</t>
+          <t>-46,95; 169,07</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>106,27; 717,11</t>
+          <t>87,56; 639,29</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 2,5</t>
+          <t>-0,65; 2,52</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>0,99; 4,77</t>
+          <t>1,1; 4,81</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1,49; 5,04</t>
+          <t>1,33; 4,99</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-2,64; -0,01</t>
+          <t>-2,78; 0,11</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>0,24; 3,91</t>
+          <t>0,31; 3,96</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,29; 4,83</t>
+          <t>1,23; 4,99</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 0,73</t>
+          <t>-1,39; 0,73</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>1,08; 3,65</t>
+          <t>1,11; 3,78</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>1,86; 4,41</t>
+          <t>1,82; 4,57</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-30,3; 154,55</t>
+          <t>-26,67; 173,05</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>22,01; 305,45</t>
+          <t>35,41; 337,16</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>44,25; 343,91</t>
+          <t>35,65; 337,08</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-76,48; 7,11</t>
+          <t>-76,8; 11,51</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>5,83; 202,8</t>
+          <t>1,29; 197,57</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>35,55; 239,55</t>
+          <t>33,31; 259,85</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-46,46; 37,6</t>
+          <t>-46,86; 36,23</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>35,97; 184,39</t>
+          <t>37,86; 204,28</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>58,08; 229,53</t>
+          <t>56,49; 225,4</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2A_ner_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P2A_ner_R-Provincia-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-6,11</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-2,39</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-8,31</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-2,26</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>5,17</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-3,66</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-6,11</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-2,39</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-8,31</t>
+          <t>-3,32</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-6,07</t>
+          <t>-5,93</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,82; 6,47</t>
+          <t>-14,03; 2,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 14,59</t>
+          <t>-10,35; 6,77</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-10,33; 0,75</t>
+          <t>-16,6; -2,91</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-14,67; 1,32</t>
+          <t>-8,29; 6,42</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-11,47; 5,81</t>
+          <t>-3,42; 14,44</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-17,87; -3,82</t>
+          <t>-11,0; 0,82</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-9,2; 1,06</t>
+          <t>-9,45; 1,73</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-4,51; 7,18</t>
+          <t>-5,03; 7,46</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-11,35; -2,77</t>
+          <t>-10,74; -2,42</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-73,48%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-28,74%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-43,8%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>100,14%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-70,91%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-73,48%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-28,74%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>-64,35%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-89,38%</t>
+          <t>-87,31%</t>
         </is>
       </c>
     </row>
@@ -783,12 +783,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-48,12; 658,23</t>
+          <t>-84,36; 220,55</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 237,14</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-85,47; 226,82</t>
+          <t>-54,47; 687,63</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 87,9</t>
+          <t>-100,0; 92,71</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-51,05; 182,14</t>
+          <t>-53,49; 196,66</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -47,79</t>
+          <t>-100,0; -34,72</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-1,98</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3,22</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1,86</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>1,68</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>3,62</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>2,27</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-1,98</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>3,22</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,99</t>
+          <t>3,32</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2,13</t>
+          <t>2,55</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 7,45</t>
+          <t>-6,85; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 9,13</t>
+          <t>-1,2; 8,62</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 7,0</t>
+          <t>-1,84; 5,41</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,97; 0,0</t>
+          <t>-2,21; 7,2</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 8,68</t>
+          <t>-0,8; 8,62</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 5,26</t>
+          <t>-0,92; 7,89</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 2,5</t>
+          <t>-2,69; 2,45</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,15; 7,37</t>
+          <t>0,24; 7,01</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 4,77</t>
+          <t>-0,58; 5,42</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>162,92%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>94,23%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>91,57%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>197,43%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>123,89%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>162,92%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>100,41%</t>
+          <t>180,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>111,88%</t>
+          <t>133,79%</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-60,95; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-68,85; —</t>
+          <t>-67,37; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1019,27 +1019,27 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-69,33; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-60,05; —</t>
+          <t>-63,62; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 472,5</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-23,97; 1011,4</t>
+          <t>-15,44; 984,67</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-32,0; 773,52</t>
+          <t>-26,73; 903,68</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-0,93</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>4,48</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>4,53</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-1,05</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>0,39</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>1,0</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-0,93</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>4,48</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,4</t>
+          <t>0,93</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2,82</t>
+          <t>2,77</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,81; 0,0</t>
+          <t>-5,32; 0,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 5,71</t>
+          <t>0,2; 10,82</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 5,27</t>
+          <t>0,8; 10,41</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,7; 0,0</t>
+          <t>-7,03; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,49; 10,87</t>
+          <t>-2,11; 4,65</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,58; 10,72</t>
+          <t>-2,1; 4,84</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 0,0</t>
+          <t>-3,29; 0,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 6,35</t>
+          <t>-0,14; 6,05</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,14; 6,23</t>
+          <t>-0,01; 5,92</t>
         </is>
       </c>
     </row>
@@ -1167,34 +1167,34 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>479,02%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>484,34%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>37,27%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>95,1%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>89,11%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>479,02%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>471,01%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
           <t>259,01%</t>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>284,61%</t>
+          <t>280,22%</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-72,84; —</t>
+          <t>-72,38; —</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-45,78; —</t>
+          <t>-51,94; —</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>2,49</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>10,04</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-2,04</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>4,86</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>6,0</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0,78</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>2,49</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>10,04</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-2,04</t>
+          <t>1,02</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-0,71</t>
+          <t>-0,54</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,88</t>
+          <t>-2,29; 8,21</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,46; 13,98</t>
+          <t>2,12; 20,86</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 4,38</t>
+          <t>-7,59; 0,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 9,03</t>
+          <t>0,01; 12,41</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,13; 20,51</t>
+          <t>0,26; 14,08</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-6,44; 0,0</t>
+          <t>-2,67; 5,06</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 8,27</t>
+          <t>0,22; 8,35</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,18; 14,13</t>
+          <t>3,47; 14,6</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 1,26</t>
+          <t>-3,22; 1,74</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>122,04%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>492,46%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>374,75%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>462,27%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>59,87%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>122,04%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>492,46%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>78,64%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-41,88%</t>
+          <t>-31,99%</t>
         </is>
       </c>
     </row>
@@ -1431,12 +1431,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-22,58; —</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-30,16; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1461,12 +1461,12 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-25,37; 1351,26</t>
+          <t>-41,52; inf</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>44,03; 2791,22</t>
+          <t>60,94; 2243,69</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>2,63</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>5,64</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>1,44</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>6,16</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>1,85</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-4,86</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>2,63</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>5,64</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,48</t>
+          <t>-4,91</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-1,41</t>
+          <t>-1,45</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-12,94; 22,95</t>
+          <t>0,0; 12,19</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-18,01; 12,71</t>
+          <t>1,68; 14,88</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-26,78; 3,3</t>
+          <t>0,0; 7,53</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,33</t>
+          <t>-12,84; 22,1</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,68; 15,27</t>
+          <t>-21,71; 10,74</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,85</t>
+          <t>-26,49; 3,15</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-5,88; 12,01</t>
+          <t>-4,55; 11,96</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-5,27; 10,41</t>
+          <t>-5,24; 10,56</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-12,39; 2,4</t>
+          <t>-11,3; 2,34</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>94,47%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>28,41%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-74,55%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>inf%</t>
+          <t>-75,3%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-47,49%</t>
+          <t>-48,76%</t>
         </is>
       </c>
     </row>
@@ -1704,32 +1704,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>-2,36</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>2,13</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>1,08</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>2,77</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>5,24</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>3,93</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>-2,36</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>2,13</t>
-        </is>
-      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,63</t>
+          <t>3,88</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2,17</t>
+          <t>2,41</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,95</t>
+          <t>-7,16; 0,0</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,26</t>
+          <t>-3,44; 11,73</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1,1; 10,63</t>
+          <t>-3,66; 6,37</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-8,28; 0,0</t>
+          <t>0,0; 10,13</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 11,83</t>
+          <t>0,0; 16,17</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 5,14</t>
+          <t>1,16; 11,14</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 2,97</t>
+          <t>-2,49; 2,65</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 10,3</t>
+          <t>0,39; 10,27</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 5,71</t>
+          <t>-0,69; 6,1</t>
         </is>
       </c>
     </row>
@@ -1810,34 +1810,34 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>90,57%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>45,68%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>90,57%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>26,9%</t>
-        </is>
-      </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
           <t>5,2%</t>
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>174,24%</t>
+          <t>193,13%</t>
         </is>
       </c>
     </row>
@@ -1898,12 +1898,12 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-55,99; —</t>
+          <t>-78,13; —</t>
         </is>
       </c>
     </row>
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>-0,77</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>-0,67</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>5,83</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>-0,12</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>2,06</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>4,42</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>-0,77</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>-0,67</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,51</t>
+          <t>4,93</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>5,09</t>
+          <t>5,45</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 2,18</t>
+          <t>-3,93; 2,07</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 6,14</t>
+          <t>-4,23; 1,82</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1,0; 8,6</t>
+          <t>1,43; 11,24</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 1,99</t>
+          <t>-2,57; 2,22</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-4,2; 1,95</t>
+          <t>-0,74; 6,24</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,03; 11,23</t>
+          <t>1,18; 9,22</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 1,58</t>
+          <t>-2,46; 1,33</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 3,05</t>
+          <t>-1,72; 2,82</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>2,11; 8,55</t>
+          <t>2,28; 9,01</t>
         </is>
       </c>
     </row>
@@ -2026,32 +2026,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>-31,56%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>-27,28%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>239,01%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>-9,1%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>161,91%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>347,91%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>-31,56%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>-27,28%</t>
-        </is>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>225,94%</t>
+          <t>387,57%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>274,48%</t>
+          <t>293,81%</t>
         </is>
       </c>
     </row>
@@ -2079,17 +2079,17 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 239,49</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 356,37</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-11,45; —</t>
+          <t>4,27; 1184,05</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -2099,27 +2099,27 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-79,33; —</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2,96; 1221,11</t>
+          <t>-2,28; —</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-81,69; 268,8</t>
+          <t>-81,61; 205,49</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-54,31; 388,12</t>
+          <t>-60,27; 308,07</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>65,68; 1107,71</t>
+          <t>55,21; 992,06</t>
         </is>
       </c>
     </row>
@@ -2136,32 +2136,32 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>-1,9</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>0,64</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>10,03</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>-1,01</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>0,18</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>9,24</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>-1,9</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>0,64</t>
-        </is>
-      </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>10,14</t>
+          <t>8,93</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>9,7</t>
+          <t>9,5</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-5,69; 2,9</t>
+          <t>-5,81; 0,58</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-4,26; 4,11</t>
+          <t>-3,67; 3,97</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>4,02; 15,53</t>
+          <t>4,47; 15,78</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-5,37; 0,6</t>
+          <t>-5,02; 3,16</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-3,33; 4,05</t>
+          <t>-4,33; 4,15</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>5,02; 15,59</t>
+          <t>3,15; 15,64</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-4,52; 0,68</t>
+          <t>-4,22; 0,95</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 3,26</t>
+          <t>-2,65; 2,95</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>5,87; 13,8</t>
+          <t>5,69; 13,78</t>
         </is>
       </c>
     </row>
@@ -2242,32 +2242,32 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>-64,38%</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>21,62%</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>340,68%</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>-24,4%</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>4,25%</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>223,45%</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>-64,38%</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>21,62%</t>
-        </is>
-      </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>344,47%</t>
+          <t>216,0%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>275,62%</t>
+          <t>269,93%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-83,32; 226,07</t>
+          <t>-100,0; 156,31</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-68,26; 225,91</t>
+          <t>-71,91; 309,91</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>43,94; 897,62</t>
+          <t>57,9; 1163,54</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 169,02</t>
+          <t>-82,51; 207,43</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-69,62; 356,66</t>
+          <t>-65,03; 242,1</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>74,26; 1227,14</t>
+          <t>33,11; 729,44</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-83,13; 45,33</t>
+          <t>-81,61; 61,61</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-46,95; 169,07</t>
+          <t>-52,47; 138,69</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>87,56; 639,29</t>
+          <t>97,0; 652,07</t>
         </is>
       </c>
     </row>
@@ -2352,32 +2352,32 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>-1,36</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>2,01</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>3,31</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>0,79</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>2,82</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>3,23</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>-1,36</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>2,01</t>
-        </is>
-      </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>3,02</t>
+          <t>3,74</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>3,13</t>
+          <t>3,52</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 2,52</t>
+          <t>-2,86; -0,02</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>1,1; 4,81</t>
+          <t>0,29; 3,88</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1,33; 4,99</t>
+          <t>1,39; 5,46</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 0,11</t>
+          <t>-0,74; 2,54</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>0,31; 3,96</t>
+          <t>1,05; 4,86</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,23; 4,99</t>
+          <t>1,77; 5,51</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 0,73</t>
+          <t>-1,34; 0,74</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>1,11; 3,78</t>
+          <t>1,19; 3,81</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>1,82; 4,57</t>
+          <t>2,2; 4,93</t>
         </is>
       </c>
     </row>
@@ -2458,32 +2458,32 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>-49,76%</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>73,52%</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>120,94%</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>36,1%</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>128,97%</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>147,72%</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>-49,76%</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>73,52%</t>
-        </is>
-      </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>110,54%</t>
+          <t>171,21%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>126,91%</t>
+          <t>142,73%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-26,67; 173,05</t>
+          <t>-79,12; 3,74</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>35,41; 337,16</t>
+          <t>4,51; 207,97</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>35,65; 337,08</t>
+          <t>33,89; 288,52</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-76,8; 11,51</t>
+          <t>-26,92; 162,54</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>1,29; 197,57</t>
+          <t>31,39; 321,6</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>33,31; 259,85</t>
+          <t>51,6; 361,0</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-46,86; 36,23</t>
+          <t>-44,46; 38,9</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>37,86; 204,28</t>
+          <t>38,33; 195,61</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>56,49; 225,4</t>
+          <t>72,17; 249,98</t>
         </is>
       </c>
     </row>
